--- a/sheets/Libetee_楽天_8月作戦.xlsx
+++ b/sheets/Libetee_楽天_8月作戦.xlsx
@@ -19,12 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="m/d(aaa)"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="¥#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot;%&quot;"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="m/d(aaa)"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="¥#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -117,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -139,18 +138,62 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,13 +202,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,13 +217,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,13 +232,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,13 +247,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,28 +262,28 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -249,25 +292,25 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -306,6 +349,84 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -742,7 +863,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="59" t="n">
         <v>46235</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -756,10 +877,10 @@
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="60" t="n">
         <v>1.68</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="61" t="n">
         <v>1243373</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -774,7 +895,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="62" t="n">
         <v>46236</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -788,10 +909,10 @@
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -806,7 +927,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="62" t="n">
         <v>46237</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -820,10 +941,10 @@
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -838,7 +959,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="65" t="n">
         <v>46238</v>
       </c>
       <c r="B7" s="15" t="inlineStr">
@@ -852,10 +973,10 @@
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="66" t="n">
         <v>1.18</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="67" t="n">
         <v>873322</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -870,7 +991,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="68" t="n">
         <v>46239</v>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -888,10 +1009,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="69" t="n">
         <v>3.01</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="70" t="n">
         <v>2227710</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -906,7 +1027,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="65" t="n">
         <v>46240</v>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -920,10 +1041,10 @@
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="66" t="n">
         <v>1.18</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="67" t="n">
         <v>873322</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -938,7 +1059,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="65" t="n">
         <v>46241</v>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -952,10 +1073,10 @@
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr"/>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="66" t="n">
         <v>1.18</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="67" t="n">
         <v>873322</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -970,7 +1091,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="65" t="n">
         <v>46242</v>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -984,10 +1105,10 @@
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr"/>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="66" t="n">
         <v>1.18</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="67" t="n">
         <v>873322</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -1002,7 +1123,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="65" t="n">
         <v>46243</v>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -1016,10 +1137,10 @@
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr"/>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="66" t="n">
         <v>1.18</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="67" t="n">
         <v>873322</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -1034,7 +1155,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="68" t="n">
         <v>46244</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -1052,10 +1173,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="69" t="n">
         <v>3.01</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="70" t="n">
         <v>2227710</v>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -1070,7 +1191,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="65" t="n">
         <v>46245</v>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -1084,10 +1205,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr"/>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="66" t="n">
         <v>1.18</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="67" t="n">
         <v>873322</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -1102,7 +1223,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="62" t="n">
         <v>46246</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1116,10 +1237,10 @@
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -1134,7 +1255,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="62" t="n">
         <v>46247</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1148,10 +1269,10 @@
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1166,7 +1287,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="62" t="n">
         <v>46248</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1180,10 +1301,10 @@
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -1198,7 +1319,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="71" t="n">
         <v>46249</v>
       </c>
       <c r="B18" s="25" t="inlineStr">
@@ -1216,10 +1337,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="72" t="n">
         <v>2.06</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="73" t="n">
         <v>1524612</v>
       </c>
       <c r="G18" s="25" t="inlineStr">
@@ -1234,7 +1355,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="62" t="n">
         <v>46250</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1248,10 +1369,10 @@
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -1266,7 +1387,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="62" t="n">
         <v>46251</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1280,10 +1401,10 @@
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1298,7 +1419,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="62" t="n">
         <v>46252</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1312,10 +1433,10 @@
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -1330,7 +1451,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="62" t="n">
         <v>46253</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1344,10 +1465,10 @@
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -1362,7 +1483,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="71" t="n">
         <v>46254</v>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -1380,10 +1501,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="72" t="n">
         <v>2.06</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="73" t="n">
         <v>1524612</v>
       </c>
       <c r="G23" s="25" t="inlineStr">
@@ -1398,7 +1519,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="62" t="n">
         <v>46255</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1412,10 +1533,10 @@
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -1430,7 +1551,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="62" t="n">
         <v>46256</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1444,10 +1565,10 @@
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -1462,7 +1583,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n">
+      <c r="A26" s="62" t="n">
         <v>46257</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -1476,10 +1597,10 @@
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -1494,7 +1615,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="62" t="n">
         <v>46258</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1508,10 +1629,10 @@
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -1526,7 +1647,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="n">
+      <c r="A28" s="71" t="n">
         <v>46259</v>
       </c>
       <c r="B28" s="25" t="inlineStr">
@@ -1544,10 +1665,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="72" t="n">
         <v>2.06</v>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="73" t="n">
         <v>1524612</v>
       </c>
       <c r="G28" s="25" t="inlineStr">
@@ -1562,7 +1683,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="62" t="n">
         <v>46260</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1576,10 +1697,10 @@
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -1594,7 +1715,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="62" t="n">
         <v>46261</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -1608,10 +1729,10 @@
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -1626,7 +1747,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="62" t="n">
         <v>46262</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1640,10 +1761,10 @@
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -1658,7 +1779,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="62" t="n">
         <v>46263</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -1672,10 +1793,10 @@
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -1690,7 +1811,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="n">
+      <c r="A33" s="71" t="n">
         <v>46264</v>
       </c>
       <c r="B33" s="25" t="inlineStr">
@@ -1708,10 +1829,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E33" s="72" t="n">
         <v>2.06</v>
       </c>
-      <c r="F33" s="28" t="n">
+      <c r="F33" s="73" t="n">
         <v>1524612</v>
       </c>
       <c r="G33" s="25" t="inlineStr">
@@ -1726,7 +1847,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
+      <c r="A34" s="62" t="n">
         <v>46265</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -1740,10 +1861,10 @@
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="64" t="n">
         <v>740103</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -1763,11 +1884,11 @@
           <t>月商予測</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="31" t="n">
+      <c r="B35" s="74" t="n"/>
+      <c r="C35" s="74" t="n"/>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="75" t="n"/>
+      <c r="F35" s="76" t="n">
         <v>30359027</v>
       </c>
       <c r="G35" s="29" t="inlineStr">
@@ -1856,16 +1977,16 @@
       <c r="B3" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="34" t="n">
+      <c r="C3" s="77" t="n">
         <v>2942893</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="78" t="n">
         <v>4.71</v>
       </c>
-      <c r="E3" s="36" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="F3" s="34" t="n">
+      <c r="E3" s="79" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F3" s="77" t="n">
         <v>29651</v>
       </c>
     </row>
@@ -1878,16 +1999,16 @@
       <c r="B4" s="38" t="n">
         <v>18</v>
       </c>
-      <c r="C4" s="39" t="n">
+      <c r="C4" s="80" t="n">
         <v>1882548</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="81" t="n">
         <v>3.01</v>
       </c>
-      <c r="E4" s="41" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F4" s="39" t="n">
+      <c r="E4" s="82" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F4" s="80" t="n">
         <v>22075</v>
       </c>
     </row>
@@ -1900,16 +2021,16 @@
       <c r="B5" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="73" t="n">
         <v>1286398</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="72" t="n">
         <v>2.06</v>
       </c>
-      <c r="E5" s="42" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F5" s="28" t="n">
+      <c r="E5" s="83" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="F5" s="73" t="n">
         <v>21277</v>
       </c>
     </row>
@@ -1922,16 +2043,16 @@
       <c r="B6" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="61" t="n">
         <v>1049789</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="60" t="n">
         <v>1.68</v>
       </c>
-      <c r="E6" s="43" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="F6" s="8" t="n">
+      <c r="E6" s="84" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F6" s="61" t="n">
         <v>21324</v>
       </c>
     </row>
@@ -1944,16 +2065,16 @@
       <c r="B7" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="67" t="n">
         <v>1018230</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="66" t="n">
         <v>1.63</v>
       </c>
-      <c r="E7" s="44" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F7" s="18" t="n">
+      <c r="E7" s="85" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="F7" s="67" t="n">
         <v>29337</v>
       </c>
     </row>
@@ -1966,16 +2087,16 @@
       <c r="B8" s="15" t="n">
         <v>54</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="67" t="n">
         <v>736866</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="66" t="n">
         <v>1.18</v>
       </c>
-      <c r="E8" s="44" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F8" s="18" t="n">
+      <c r="E8" s="85" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F8" s="67" t="n">
         <v>19103</v>
       </c>
     </row>
@@ -1988,19 +2109,20 @@
       <c r="B9" s="10" t="n">
         <v>224</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="64" t="n">
         <v>624430</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="45" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F9" s="13" t="n">
+      <c r="E9" s="86" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F9" s="64" t="n">
         <v>22093</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -2251,6 +2373,7 @@
       <c r="D15" s="49" t="n"/>
       <c r="E15" s="49" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>

--- a/sheets/Libetee_楽天_8月作戦.xlsx
+++ b/sheets/Libetee_楽天_8月作戦.xlsx
@@ -863,8 +863,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="n">
-        <v>46235</v>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>8/1(土)</t>
+        </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -895,8 +897,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="n">
-        <v>46236</v>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>8/2(日)</t>
+        </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
@@ -927,8 +931,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="62" t="n">
-        <v>46237</v>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>8/3(月)</t>
+        </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -959,8 +965,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="n">
-        <v>46238</v>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>8/4(火)</t>
+        </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
@@ -991,8 +999,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="n">
-        <v>46239</v>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>8/5(水)</t>
+        </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
@@ -1027,8 +1037,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="n">
-        <v>46240</v>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>8/6(木)</t>
+        </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
@@ -1059,8 +1071,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="n">
-        <v>46241</v>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>8/7(金)</t>
+        </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
@@ -1091,8 +1105,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="n">
-        <v>46242</v>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>8/8(土)</t>
+        </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
@@ -1123,8 +1139,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="n">
-        <v>46243</v>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>8/9(日)</t>
+        </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
@@ -1155,8 +1173,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="n">
-        <v>46244</v>
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>8/10(月)</t>
+        </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
@@ -1191,8 +1211,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="n">
-        <v>46245</v>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>8/11(火)</t>
+        </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
@@ -1223,8 +1245,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="62" t="n">
-        <v>46246</v>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>8/12(水)</t>
+        </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1255,8 +1279,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="n">
-        <v>46247</v>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>8/13(木)</t>
+        </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1287,8 +1313,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="62" t="n">
-        <v>46248</v>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>8/14(金)</t>
+        </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1319,8 +1347,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="71" t="n">
-        <v>46249</v>
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>8/15(土)</t>
+        </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
@@ -1355,8 +1385,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="62" t="n">
-        <v>46250</v>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>8/16(日)</t>
+        </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1387,8 +1419,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="62" t="n">
-        <v>46251</v>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>8/17(月)</t>
+        </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1419,8 +1453,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="62" t="n">
-        <v>46252</v>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>8/18(火)</t>
+        </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1451,8 +1487,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="n">
-        <v>46253</v>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>8/19(水)</t>
+        </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1483,8 +1521,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="71" t="n">
-        <v>46254</v>
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>8/20(木)</t>
+        </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
@@ -1519,8 +1559,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="62" t="n">
-        <v>46255</v>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>8/21(金)</t>
+        </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1551,8 +1593,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="62" t="n">
-        <v>46256</v>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>8/22(土)</t>
+        </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1583,8 +1627,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="62" t="n">
-        <v>46257</v>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>8/23(日)</t>
+        </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1615,8 +1661,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="62" t="n">
-        <v>46258</v>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1647,8 +1695,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="71" t="n">
-        <v>46259</v>
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>8/25(火)</t>
+        </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
@@ -1683,8 +1733,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="62" t="n">
-        <v>46260</v>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>8/26(水)</t>
+        </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1715,8 +1767,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="62" t="n">
-        <v>46261</v>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>8/27(木)</t>
+        </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1747,8 +1801,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="62" t="n">
-        <v>46262</v>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>8/28(金)</t>
+        </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -1779,8 +1835,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="62" t="n">
-        <v>46263</v>
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>8/29(土)</t>
+        </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -1811,8 +1869,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="71" t="n">
-        <v>46264</v>
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>8/30(日)</t>
+        </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
@@ -1847,8 +1907,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="62" t="n">
-        <v>46265</v>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>8/31(月)</t>
+        </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
